--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -518,7 +518,7 @@
         <v>-24.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>43.35</v>
+        <v>43.34</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>67.5</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:40</t>
+    <t xml:space="preserve">2026-10-05 04:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>39.52</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>50.58</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         <v>-24.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>43.34</v>
+        <v>43.35</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>67.5</v>
